--- a/data/trans_camb/P1426-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1426-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,11</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,18</t>
+          <t>-1,5; 3,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,09</t>
+          <t>-1,77; 2,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,15</t>
+          <t>-2,51; 2,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,53</t>
+          <t>-2,88; 1,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,37</t>
+          <t>-1,26; 2,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,16</t>
+          <t>-1,67; 1,18</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-16,58%</t>
+          <t>-18,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-6,54%</t>
+          <t>-5,41%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-65,91; 443,78</t>
+          <t>-65,0; 410,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 397,13</t>
+          <t>-67,69; 357,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 292,66</t>
+          <t>-67,04; 273,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,94; 155,37</t>
+          <t>-71,2; 158,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 175,1</t>
+          <t>-43,89; 195,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,05; 98,26</t>
+          <t>-57,39; 99,7</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,8</t>
+          <t>-1,52; 0,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,34</t>
+          <t>-0,07; 3,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,08</t>
+          <t>-3,52; 0,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,03</t>
+          <t>-2,91; 0,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,09</t>
+          <t>-2,06; 0,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,58</t>
+          <t>-0,89; 1,51</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>255,86%</t>
+          <t>260,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-28,89%</t>
+          <t>-29,94%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -868,27 +868,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,23; —</t>
+          <t>-64,73; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,9; 23,08</t>
+          <t>-90,26; 20,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 76,85</t>
+          <t>-70,61; 63,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,47; 17,65</t>
+          <t>-82,79; 16,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,04; 156,44</t>
+          <t>-39,82; 142,79</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>7,55</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,92</t>
+          <t>5,75</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,38</t>
+          <t>-3,68; 0,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 10,92</t>
+          <t>4,43; 10,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,16</t>
+          <t>-2,42; 1,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,41</t>
+          <t>1,85; 6,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,33</t>
+          <t>-2,25; 0,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,96</t>
+          <t>3,8; 7,55</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>470,5%</t>
+          <t>459,11%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>280,89%</t>
+          <t>273,31%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>374,24%</t>
+          <t>363,64%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 232,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,82; 1980,55</t>
+          <t>99,62; 1677,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 375,88</t>
+          <t>-100,0; 298,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48,12; 1109,89</t>
+          <t>47,91; 884,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,43; 85,1</t>
+          <t>-86,98; 75,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>120,63; 970,62</t>
+          <t>128,87; 877,27</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>2,02</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,42</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,43</t>
+          <t>-0,42; 3,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,33</t>
+          <t>0,38; 4,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,31</t>
+          <t>-1,85; 1,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,73</t>
+          <t>0,88; 4,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,67</t>
+          <t>-0,83; 1,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,54</t>
+          <t>1,18; 3,67</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>283,74%</t>
+          <t>244,68%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156,63%</t>
+          <t>216,74%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>206,33%</t>
+          <t>229,82%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,85; 1354,62</t>
+          <t>-67,6; 1070,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 1453,81</t>
+          <t>-15,6; 1419,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 690,0</t>
+          <t>-100,0; 323,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 742,25</t>
+          <t>15,92; 771,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,35; 314,54</t>
+          <t>-57,79; 302,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,39; 686,9</t>
+          <t>55,67; 616,34</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>3,56</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>2,94</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 0,6</t>
+          <t>-5,57; 0,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 7,99</t>
+          <t>-0,59; 7,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 2,77</t>
+          <t>-5,71; 2,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,96</t>
+          <t>-2,02; 5,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,79</t>
+          <t>-4,41; 0,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 6,05</t>
+          <t>0,09; 5,35</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>113,36%</t>
+          <t>101,08%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>64,99%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 100,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 513,56</t>
+          <t>-15,99; 385,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,68; 96,68</t>
+          <t>-72,6; 88,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 192,93</t>
+          <t>-24,94; 189,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,72; 35,63</t>
+          <t>-73,25; 43,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,17; 182,85</t>
+          <t>0,03; 179,99</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10,42</t>
+          <t>10,51</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10,73</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,4</t>
+          <t>-4,06; 1,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,32</t>
+          <t>6,58; 14,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,91</t>
+          <t>-0,99; 4,26</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7,17; 13,8</t>
+          <t>7,6; 13,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,95</t>
+          <t>-1,65; 1,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,97; 12,87</t>
+          <t>8,04; 12,97</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>344,67%</t>
+          <t>347,65%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>698,68%</t>
+          <t>694,36%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>465,91%</t>
+          <t>466,2%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-81,33; 141,61</t>
+          <t>-86,67; 122,91</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>123,46; 1000,92</t>
+          <t>121,77; 939,97</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 730,93</t>
+          <t>-59,22; 726,72</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>197,01; 2973,48</t>
+          <t>202,92; 2873,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-55,55; 144,06</t>
+          <t>-55,42; 139,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>219,85; 925,4</t>
+          <t>231,35; 998,5</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>4,16</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,25</t>
+          <t>-2,03; 1,12</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,25</t>
+          <t>1,05; 5,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,84</t>
+          <t>0,96; 4,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 6,01</t>
+          <t>3,32; 7,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 2,59</t>
+          <t>-0,01; 2,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,89</t>
+          <t>2,89; 5,6</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>122,98%</t>
+          <t>128,31%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>237,64%</t>
+          <t>336,59%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>167,79%</t>
+          <t>211,53%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-61,36; 96,51</t>
+          <t>-60,51; 81,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24,28; 348,47</t>
+          <t>25,77; 330,67</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36,44; 581,51</t>
+          <t>29,36; 503,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30,04; 590,75</t>
+          <t>131,87; 760,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 172,82</t>
+          <t>-3,11; 177,55</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,22; 328,98</t>
+          <t>108,15; 410,35</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,4</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,6</t>
+          <t>-0,21; 1,67</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,12</t>
+          <t>0,34; 2,58</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,52</t>
+          <t>-1,13; 0,64</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,62</t>
+          <t>0,34; 2,5</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,85</t>
+          <t>-0,52; 0,8</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,9</t>
+          <t>0,67; 2,16</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>172,59%</t>
+          <t>249,73%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>154,59%</t>
+          <t>149,06%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>151,63%</t>
+          <t>184,72%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-41,03; 927,95</t>
+          <t>-40,85; 1015,25</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 1086,73</t>
+          <t>9,93; 1301,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-84,72; 157,08</t>
+          <t>-80,64; 187,18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6,22; 603,84</t>
+          <t>11,75; 528,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 203,38</t>
+          <t>-51,07; 166,65</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,72; 422,58</t>
+          <t>55,09; 491,59</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,97</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,46</t>
+          <t>-0,72; 0,51</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,76</t>
+          <t>2,38; 3,85</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,89</t>
+          <t>-0,54; 0,86</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,3</t>
+          <t>2,11; 3,48</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,43</t>
+          <t>-0,43; 0,55</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,41</t>
+          <t>2,4; 3,49</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>189,51%</t>
+          <t>201,88%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>136,81%</t>
+          <t>152,53%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>160,23%</t>
+          <t>174,49%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 36,29</t>
+          <t>-38,84; 44,58</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>97,18; 293,7</t>
+          <t>122,68; 321,49</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 58,11</t>
+          <t>-24,7; 52,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>72,18; 220,99</t>
+          <t>92,83; 231,4</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 28,41</t>
+          <t>-22,76; 36,34</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>107,48; 230,77</t>
+          <t>118,05; 238,58</t>
         </is>
       </c>
     </row>
